--- a/artfynd/A 24998-2026 artfynd.xlsx
+++ b/artfynd/A 24998-2026 artfynd.xlsx
@@ -675,50 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1976814</v>
+        <v>1906629</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80367</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6457</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kärmsjöhöjdens NV-sluttning, SV Stor-Kärmsjön, 23 km NV Junsele k:a, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582627.9833905026</v>
+        <v>582628</v>
       </c>
       <c r="R2" t="n">
-        <v>7085455.997189353</v>
+        <v>7085456</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,26 +748,16 @@
           <t>2011-08-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2011-08-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -779,7 +769,17 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>på sälg (80 cm i dbh)</t>
+          <t>på bark på N-sidan av sälg (minst 120 år, 80 cm i dbh)</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>5921</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,37 +797,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6563564</v>
+        <v>1976814</v>
       </c>
       <c r="B3" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582627.9833905026</v>
+        <v>582628</v>
       </c>
       <c r="R3" t="n">
-        <v>7085455.997189353</v>
+        <v>7085456</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,19 +865,9 @@
           <t>2011-08-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2011-08-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,15 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1906629</v>
+        <v>6563564</v>
       </c>
       <c r="B4" t="n">
-        <v>78458</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,39 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6457</v>
+        <v>229497</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kärmsjöhöjdens NV-sluttning, SV Stor-Kärmsjön, 23 km NV Junsele k:a, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582627.9833905026</v>
+        <v>582628</v>
       </c>
       <c r="R4" t="n">
-        <v>7085455.997189353</v>
+        <v>7085456</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,26 +972,16 @@
           <t>2011-08-30</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2011-08-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="b">
         <v>0</v>
@@ -1028,17 +993,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>på bark på N-sidan av sälg (minst 120 år, 80 cm i dbh)</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>Fredrik Jonsson</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>5921</t>
+          <t>på sälg (80 cm i dbh)</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 24998-2026 artfynd.xlsx
+++ b/artfynd/A 24998-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -794,6 +799,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1906629</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1976814</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,8 +1023,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6563564</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>